--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486702_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486702_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.3878</v>
+        <v>10.0459</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7437</v>
+        <v>5.9232</v>
       </c>
       <c r="F2" t="n">
-        <v>4.6441</v>
+        <v>4.1226</v>
       </c>
       <c r="G2" t="n">
         <v>4.7466</v>
@@ -610,13 +610,13 @@
         <v>2.7031</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3556</v>
+        <v>1.0137</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4956</v>
+        <v>-0.3249</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.3385</v>
       </c>
       <c r="V2" t="n">
         <v>2.741</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.13</v>
+        <v>3.9467</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8237</v>
+        <v>1.417</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3063</v>
+        <v>2.5297</v>
       </c>
       <c r="G3" t="n">
         <v>0.0959</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7831</v>
+        <v>0.5998</v>
       </c>
       <c r="T3" t="n">
-        <v>0.22</v>
+        <v>-0.1867</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.7865</v>
       </c>
       <c r="V3" t="n">
         <v>1.5133</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2879</v>
+        <v>3.1167</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3</v>
+        <v>0.2241</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5879</v>
+        <v>2.8926</v>
       </c>
       <c r="G4" t="n">
         <v>0.7445000000000001</v>
@@ -766,13 +766,13 @@
         <v>2.1239</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6127</v>
+        <v>0.4415</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.1313</v>
+        <v>-0.6072</v>
       </c>
       <c r="U4" t="n">
-        <v>1.744</v>
+        <v>1.0487</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3971</v>
+        <v>1.8966</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5552</v>
+        <v>-0.1688</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8419</v>
+        <v>2.0654</v>
       </c>
       <c r="G5" t="n">
         <v>-2.7792</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9486</v>
+        <v>0.4481</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7994</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1492</v>
+        <v>0.3727</v>
       </c>
       <c r="V5" t="n">
         <v>3.0692</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0531</v>
+        <v>1.4627</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7175</v>
+        <v>-0.4072</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7706</v>
+        <v>1.8699</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1383</v>
@@ -922,13 +922,13 @@
         <v>0.7723</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2373</v>
+        <v>0.1723</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3037</v>
+        <v>0.0066</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0663</v>
+        <v>0.1657</v>
       </c>
       <c r="V6" t="n">
         <v>0.6565</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0242</v>
+        <v>0.5095</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1388</v>
+        <v>-0.8285</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1146</v>
+        <v>1.3381</v>
       </c>
       <c r="G7" t="n">
         <v>-0.0254</v>
@@ -1000,13 +1000,13 @@
         <v>1.9308</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4855</v>
+        <v>0.0482</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9107</v>
+        <v>-0.6004</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4251</v>
+        <v>0.6486</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2856</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06759999999999999</v>
+        <v>0.2716</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0115</v>
+        <v>-0.5978</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9439</v>
+        <v>0.8694</v>
       </c>
       <c r="G8" t="n">
         <v>-0.0217</v>
@@ -1078,13 +1078,13 @@
         <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0772</v>
+        <v>0.262</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5796</v>
+        <v>-0.1659</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5024</v>
+        <v>0.4279</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5133</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. VALERO PRIETO</t>
+          <t>G. ZALAZAR RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0953</v>
+        <v>0.1991</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1449</v>
+        <v>-0.0589</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0495</v>
+        <v>0.258</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1584</v>
+        <v>-0.5691000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0205</v>
+        <v>-0.7794</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1379</v>
+        <v>0.2102</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0207</v>
+        <v>-0.0921</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0207</v>
+        <v>0.3939</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.486</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1377</v>
+        <v>-0.477</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0002</v>
+        <v>-1.1733</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1379</v>
+        <v>0.6962</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2538</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1655</v>
+        <v>-0.6072</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0882</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.7989</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TEVAR TEVAR</t>
+          <t>J. VALERO PRIETO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3173</v>
+        <v>-0.0209</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1104</v>
+        <v>-0.1449</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2069</v>
+        <v>0.124</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.1584</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.0205</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.1379</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.0207</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.0207</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.1377</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0002</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.1379</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2483</v>
+        <v>-0.1793</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1104</v>
+        <v>-0.1655</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1379</v>
+        <v>-0.0137</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. ZALAZAR RODRIGUEZ</t>
+          <t>M. TEVAR TEVAR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5484</v>
+        <v>-0.3173</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5829</v>
+        <v>-0.1104</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0345</v>
+        <v>-0.2069</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7794</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2102</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0921</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3939</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.486</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.477</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1733</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.6962</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7377</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8442</v>
+        <v>-0.2483</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1313</v>
+        <v>-0.1104</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2871</v>
+        <v>-0.1379</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.7989</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>F. GARRIDO PARDO</t>
+          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9722</v>
+        <v>-1.4508</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7652</v>
+        <v>-0.1467</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2069</v>
+        <v>-1.3041</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7585</v>
+        <v>0.17</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.5105</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6895</v>
+        <v>0.6805</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.6895</v>
+        <v>0.9224</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.3865</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6895</v>
+        <v>0.5359</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.7524</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.897</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.1447</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9654</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2483</v>
+        <v>-0.007</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1104</v>
+        <v>-0.1037</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1379</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. CAÑAS-BALIÑA MENGIBAR</t>
+          <t>F. GARRIDO PARDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0949</v>
+        <v>-1.9722</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5673</v>
+        <v>-1.7652</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5276</v>
+        <v>-0.2069</v>
       </c>
       <c r="G13" t="n">
-        <v>0.17</v>
+        <v>-0.7585</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5105</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6805</v>
+        <v>-0.6895</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9224</v>
+        <v>-0.6895</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3865</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5359</v>
+        <v>-0.6895</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7524</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.897</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1447</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6511</v>
+        <v>-0.2483</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5243</v>
+        <v>-0.1104</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1268</v>
+        <v>-0.1379</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>17.136</v>
+        <v>17.6876</v>
       </c>
       <c r="E14" t="n">
-        <v>2.784099999999998</v>
+        <v>3.3359</v>
       </c>
       <c r="F14" t="n">
-        <v>14.3519</v>
+        <v>14.3518</v>
       </c>
       <c r="G14" t="n">
         <v>1.5542</v>
@@ -1528,7 +1528,7 @@
         <v>-1.615699999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>0.4042999999999999</v>
+        <v>0.4042999999999998</v>
       </c>
       <c r="N14" t="n">
         <v>-4.4898</v>
@@ -1546,13 +1546,13 @@
         <v>14.4808</v>
       </c>
       <c r="S14" t="n">
-        <v>1.654300000000001</v>
+        <v>2.2061</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.452199999999999</v>
+        <v>-2.9003</v>
       </c>
       <c r="U14" t="n">
-        <v>5.106299999999999</v>
+        <v>5.106400000000001</v>
       </c>
       <c r="V14" t="n">
         <v>5.239000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7775</v>
+        <v>2.4161</v>
       </c>
       <c r="E15" t="n">
-        <v>0.862</v>
+        <v>0.4483</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9155</v>
+        <v>1.9679</v>
       </c>
       <c r="G15" t="n">
         <v>2.0918</v>
@@ -1624,13 +1624,13 @@
         <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8442</v>
+        <v>0.4828</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4972</v>
+        <v>-0.9109</v>
       </c>
       <c r="U15" t="n">
-        <v>1.3414</v>
+        <v>1.3937</v>
       </c>
       <c r="V15" t="n">
         <v>0.6138</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1791</v>
+        <v>1.4411</v>
       </c>
       <c r="E16" t="n">
         <v>0.6966</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4825</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>1.317</v>
@@ -1702,13 +1702,13 @@
         <v>0.1931</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.331</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0551</v>
+        <v>0.2069</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0525</v>
+        <v>0.1103</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0525</v>
+        <v>0.1103</v>
       </c>
       <c r="G17" t="n">
         <v>0.0689</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1213</v>
+        <v>0.0414</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1213</v>
+        <v>0.0414</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1187</v>
+        <v>-0.0553</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1187</v>
+        <v>-0.0553</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0692</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0495</v>
+        <v>0.0139</v>
       </c>
       <c r="T18" t="n">
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0495</v>
+        <v>0.0139</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SANCHEZ CASTILLO</t>
+          <t>A. DELICADO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5357</v>
+        <v>-0.0898</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4897</v>
+        <v>0.7948</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0459</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3382</v>
+        <v>1.3598</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3377</v>
+        <v>0.7857</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6758999999999999</v>
+        <v>0.5742</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6274</v>
+        <v>2.0101</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0621</v>
+        <v>1.4766</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6895</v>
+        <v>0.5336</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2892</v>
+        <v>-0.6503</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2756</v>
+        <v>-0.6909</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0135</v>
+        <v>0.0406</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0882</v>
+        <v>0.4345</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1377</v>
+        <v>-0.8211000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0495</v>
+        <v>1.2557</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.2856</v>
+        <v>-1.8842</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5712</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2856</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. DELICADO DOMINGUEZ</t>
+          <t>R. SANCHEZ CASTILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1418</v>
+        <v>-0.7618</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0709</v>
+        <v>-0.9034</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2127</v>
+        <v>0.1416</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3598</v>
+        <v>-0.3382</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7857</v>
+        <v>0.3377</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5742</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0101</v>
+        <v>-0.6274</v>
       </c>
       <c r="K20" t="n">
-        <v>1.4766</v>
+        <v>0.0621</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5336</v>
+        <v>-0.6895</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6503</v>
+        <v>0.2892</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6909</v>
+        <v>0.2756</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0406</v>
+        <v>0.0135</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9654</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6175</v>
+        <v>-0.138</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5451</v>
+        <v>-0.276</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9276</v>
+        <v>0.1381</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8842</v>
+        <v>-0.2856</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5712</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4554</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2485</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0897</v>
+        <v>0.0137</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1588</v>
+        <v>-0.9961</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5933</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3696</v>
+        <v>-0.1035</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2592</v>
+        <v>-0.0965</v>
       </c>
       <c r="V21" t="n">
         <v>-0.2856</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. DIAZ CARBALLO</t>
+          <t>A. RUPÉREZ VÁZQUEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5792</v>
+        <v>-1.3792</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2165</v>
+        <v>-1.7308</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3627</v>
+        <v>0.3515</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8022</v>
+        <v>-0.4346</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0411</v>
+        <v>-0.5792</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8433</v>
+        <v>0.1447</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6061</v>
+        <v>-0.6481</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5247000000000001</v>
+        <v>-0.6481</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0814</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4083</v>
+        <v>0.2135</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4837</v>
+        <v>0.0689</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9247</v>
+        <v>0.1447</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9654</v>
+        <v>0.1931</v>
       </c>
       <c r="S22" t="n">
-        <v>1.721</v>
+        <v>-0.1724</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7993</v>
+        <v>-0.1173</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9218</v>
+        <v>-0.0551</v>
       </c>
       <c r="V22" t="n">
-        <v>-2.498</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. RUPÉREZ VÁZQUEZ</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.582</v>
+        <v>-2.1426</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8342</v>
+        <v>-2.3518</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2522</v>
+        <v>0.2092</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.4346</v>
+        <v>-1.6158</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5792</v>
+        <v>-0.3521</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1447</v>
+        <v>-1.2637</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6481</v>
+        <v>-1.5104</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6481</v>
+        <v>0.4767</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.9871</v>
       </c>
       <c r="M23" t="n">
-        <v>0.2135</v>
+        <v>-0.1055</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0689</v>
+        <v>-0.8288</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1447</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="P23" t="n">
         <v>-0.7723</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3751</v>
+        <v>0.5311</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2207</v>
+        <v>-0.7522</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1544</v>
+        <v>1.2833</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>A. DIAZ CARBALLO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2376</v>
+        <v>-2.3969</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4552</v>
+        <v>-1.1473</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2176</v>
+        <v>-1.2496</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.6158</v>
+        <v>-0.8022</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3521</v>
+        <v>0.0411</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.2637</v>
+        <v>-0.8433</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5104</v>
+        <v>0.6061</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4767</v>
+        <v>0.5247000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9871</v>
+        <v>0.0814</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1055</v>
+        <v>-1.4083</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8288</v>
+        <v>-0.4837</v>
       </c>
       <c r="O24" t="n">
-        <v>0.7233000000000001</v>
+        <v>-0.9247</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4362</v>
+        <v>0.9033</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8556</v>
+        <v>-0.1315</v>
       </c>
       <c r="U24" t="n">
-        <v>1.2918</v>
+        <v>1.0348</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.2856</v>
+        <v>-2.498</v>
       </c>
       <c r="W24" t="n">
-        <v>1.8415</v>
+        <v>-0.6565</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1271</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7684</v>
+        <v>-4.0167</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.0555</v>
+        <v>-2.9521</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.7129</v>
+        <v>-1.0647</v>
       </c>
       <c r="G25" t="n">
         <v>-0.2826</v>
@@ -2404,13 +2404,13 @@
         <v>0.3862</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.5172</v>
+        <v>-0.7655</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9381</v>
+        <v>-0.8347</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0.0692</v>
       </c>
       <c r="V25" t="n">
         <v>-3.3548</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.8281</v>
+        <v>-6.5208</v>
       </c>
       <c r="E26" t="n">
-        <v>-7.8403</v>
+        <v>-7.2198</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0122</v>
+        <v>0.6991000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-2.2558</v>
@@ -2482,13 +2482,13 @@
         <v>0.7723</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3625</v>
+        <v>-0.0552</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.6003</v>
+        <v>-0.9797</v>
       </c>
       <c r="U26" t="n">
-        <v>0.2378</v>
+        <v>0.9246</v>
       </c>
       <c r="V26" t="n">
         <v>2.741</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-17.1359</v>
+        <v>-14.378</v>
       </c>
       <c r="E27" t="n">
-        <v>-14.3516</v>
+        <v>-14.3518</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.7842</v>
+        <v>-0.02619999999999978</v>
       </c>
       <c r="G27" t="n">
         <v>-1.5542</v>
@@ -2560,19 +2560,19 @@
         <v>5.7925</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.6541</v>
+        <v>1.1034</v>
       </c>
       <c r="T27" t="n">
-        <v>-5.1063</v>
+        <v>-5.1062</v>
       </c>
       <c r="U27" t="n">
-        <v>3.452300000000001</v>
+        <v>6.21</v>
       </c>
       <c r="V27" t="n">
-        <v>-5.238999999999999</v>
+        <v>-5.239000000000001</v>
       </c>
       <c r="W27" t="n">
-        <v>5.6396</v>
+        <v>5.639600000000001</v>
       </c>
       <c r="X27" t="n">
         <v>-10.8787</v>
